--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0083.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0083.xlsx
@@ -784,7 +784,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Knowledge</t>
+          <t>Tri Thức</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Action</t>
+          <t>Hành động</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Teamwork</t>
+          <t>Đồng đội</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Renown</t>
+          <t>Danh Tiếng</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Rapport</t>
+          <t>Mối Quan Hệ</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Efficiency</t>
+          <t>Hiệu Suất</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Chat</t>
+          <t>Trò Chuyện</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Gift</t>
+          <t>Món quà</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Preparations</t>
+          <t>Chuẩn bị</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Travel</t>
+          <t>Du Hành</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Lời trăng dạy bảo</t>
+          <t>Lời Trăng Răn Dạy</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Plum Blossom Pole</t>
+          <t>Cột Mận Hoa</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Yumyum Haven</t>
+          <t>Thiên Đường Ẩm Thực</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Swim, Gulpuff, Swim</t>
+          <t>Bơi đi, Gulpuff, bơi lên!</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Puppet Theater</t>
+          <t>Nhà Hát Búp Bê</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Hsin's Fortuity</t>
+          <t>May mắn của Hsin</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Fan Drawing Stall</t>
+          <t>Gian Hàng Tranh Người Hâm Mộ</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Riddle Twiddle</t>
+          <t>Câu Đố Lung Tung</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Moon Shooter</t>
+          <t>Bắn Trăng</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Loong Dance</t>
+          <t>Điệu Múa Rồng</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Nâng Cấp Hoàn Tất</t>
+          <t>Nâng cấp Hoàn tất</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Building Complete</t>
+          <t>Hoàn Thành Xây Dựng</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Fund Multiplier Increased</t>
+          <t>Hệ Số Quỹ Đã Tăng</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>To Be Built</t>
+          <t>Chưa xây dựng</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Xây Dựng</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Festival Memories</t>
+          <t>Kỷ Niệm Lễ Hội</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Wish Earnings Bonus Up</t>
+          <t>Tăng Phần Thưởng Ước Nguyện</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Bonus Wish Tags</t>
+          <t>Thẻ Ước Nguyện Thưởng</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Preparation Credit Cost Down</t>
+          <t>Giảm Chi Phí Tín Dụng Chuẩn Bị</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Wish Positive Rating Chance Up</t>
+          <t>Tỷ Lệ Đánh Giá Tích Cực Tăng</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Popularity Up</t>
+          <t>Độ nổi tiếng tăng</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Wish Earnings Up</t>
+          <t>Tăng Thu Nhập Ước Nguyện</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Thời gian bên nhau: Dễ chịu</t>
+          <t>Thời gian bên nhau: Thật dễ chịu</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Hoàn thành Wish Upon the Moon IV - Swan Song để nhận</t>
+          <t>Hoàn thành Wish Upon the Moon IV - Swan Song để nhận thưởng</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Available</t>
+          <t>Có Sẵn</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Claimed</t>
+          <t>Đã nhận</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Time Together: Pleasant</t>
+          <t>Thời gian bên nhau: Dễ chịu</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Time Together: Perfect</t>
+          <t>Thời gian bên nhau: Hoàn hảo</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Đoàn tụ là kết thúc yêu thích của mọi người</t>
+          <t>Đoàn tụ là kết thúc mà ai cũng mong đợi</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Điều Ước Lều Trại</t>
+          <t>Điều Ước Nhà Trọ</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Gian hàng Hội Chợ</t>
+          <t>Gian Hàng Hội Chợ</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Companions</t>
+          <t>Đồng Hành</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Total Popularity</t>
+          <t>Tổng Độ Phổ Biến</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Total Funds</t>
+          <t>Tổng Quỹ</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Total Wishes</t>
+          <t>Tổng Số Điều Ước</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Stalls Unlocked</t>
+          <t>Các Gian Hàng Đã Mở Khóa</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Wishes Fulfilled</t>
+          <t>Điều Ước Thành Hiện Thực</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Companions Unlocked</t>
+          <t>Đã Mở Khóa Đồng Hành</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Most Completed</t>
+          <t>Hoàn Thành Nhiều Nhất</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Strongest Bond</t>
+          <t>Mối Dây Liên Kết Bền Chặt Nhất</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Most Collaborated</t>
+          <t>Cộng Tác Nhiều Nhất</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Success</t>
+          <t>Thành công</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Thất bại</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Wish Complete</t>
+          <t>Ước Nguyện Hoàn Thành</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Stall Built</t>
+          <t>Gian Hàng Đã Xây</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Stall Nâng cấp</t>
+          <t>Nâng Cấp Gian Hàng</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Mở khóa sau khi đáp ứng điều kiện</t>
+          <t>Mở khóa khi đáp ứng đủ điều kiện</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Bạn chưa xây gian hàng này</t>
+          <t>Cậu chưa dựng gian hàng này</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Lời mời khả dụng khi tất cả gian hàng được xây dựng</t>
+          <t>Có thể mời sau khi xây dựng xong tất cả các gian hàng</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Đoàn Tụ Dưới Trăng</t>
+          <t>Sum Vầy Dưới Trăng</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Wish Upon the Moon I</t>
+          <t>Nguyện Ước Trăng I</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Wish Upon the Moon: II</t>
+          <t>Nguyện Ước Trăng: II</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Wish Upon the Moon: III</t>
+          <t>Nguyện Ước Trăng: III</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Wish Upon the Moon: IV</t>
+          <t>Nguyện Ước Trăng: IV</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Moon, Be My Guest</t>
+          <t>Trăng Ơi, Hãy Ghé Thăm Ta</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Moonlit Chase</t>
+          <t>Săn Đuổi Dưới Trăng</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Theo Đuổi Vinh Quang Của Trăng</t>
+          <t>Đuổi theo vinh quang của Mặt Trăng</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Đội đã đầy, không thể thêm đồng hành</t>
+          <t>Đội đã đủ, không thể thêm đồng đội</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Đã hoàn thành</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>SOL3 Continent</t>
+          <t>Lục Địa SOL3</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Mianloong Chamber: Upper Tier</t>
+          <t>Khu Vực Mianloong: Tầng Trên</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Mianloong Chamber: Lower Tier</t>
+          <t>Khu Vực Mianloong: Tầng Dưới</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Truthseeker's Pass: Upper Tier</t>
+          <t>Thẻ Thông Hành Của Kẻ Tầm Sự Thật: Hạng Cao Cấp</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Truthseeker's Pass: Middle Tier</t>
+          <t>Thẻ Thông Hành Của Kẻ Tầm Sự Thật: Hạng Trung Cấp</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Truthseeker's Pass: Lower Tier</t>
+          <t>Thẻ Thông Hành Của Kẻ Tầm Sự Thật: Hạng Cơ Bản</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Woodveil Hall: Upper Tier</t>
+          <t>Đại Sảnh Woodveil: Tầng Trên</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Woodveil Hall: Middle Tier</t>
+          <t>Đại Sảnh Woodveil: Tầng Giữa</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -6804,7 +6804,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Woodveil Hall: Lower Tier</t>
+          <t>Đại Sảnh Woodveil: Tầng Dưới</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Meditation</t>
+          <t>Thiền định</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Elevation</t>
+          <t>Độ Cao</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Chi Flow</t>
+          <t>Dòng Chảy Chi</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Alignment</t>
+          <t>Sự đồng bộ</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Revelation</t>
+          <t>Khải Huyền</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Snowstrider's Flight</t>
+          <t>Bay Trên Tuyết</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Icy Terminus</t>
+          <t>Điểm Dừng Lạnh Giá</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Glacial Shroud</t>
+          <t>Bóng Tối Băng Giá</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Heart of Ice</t>
+          <t>Trái Tim Băng Giá</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7504,7 +7504,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Winter's Mark</t>
+          <t>Dấu Ấn Mùa Đông</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Một Hạt Giống trong Vùng Đất Hoang</t>
+          <t>Hạt Giống Trong Sa Mạc Hoang Tàn</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Tempest Spear</t>
+          <t>Ngọn Giáo Bão Tố</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Lucky Greetings Collection</t>
+          <t>Bộ Sưu Tập Lời Chúc May Mắn</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Thousandfold Tides</t>
+          <t>Sóng Ngàn Trùng</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Dusted Booklet</t>
+          <t>Cuốn Sổ Phủ Bụi</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>"Protection Fee"</t>
+          <t>"Phí bảo kê"</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Lightning Filaments</t>
+          <t>Sợi Sét</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Burst Domain</t>
+          <t>Lãnh Địa Kích Hoạt</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -8134,7 +8134,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Void Domain</t>
+          <t>Miền Hư Không</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Sacrifice</t>
+          <t>Sự Hy Sinh</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Rebellious Dark Flames</t>
+          <t>Lửa Bóng Tối Nổi Loạn</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8414,7 +8414,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Xuất sắc trong các đòn tấn công phối hợp</t>
+          <t>Xuất sắc trong Tấn Công Phối Hợp</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -8554,7 +8554,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Turtle's Reverie</t>
+          <t>Giấc Mơ Rùa</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Rabbit's Reverie</t>
+          <t>Mộng Ảo Của Rabbit</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -8694,7 +8694,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Innocent's Reverie</t>
+          <t>Mộng Ảo Ngây Thơ</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Lark's Reverie</t>
+          <t>Khúc Mộng Sơn Ca</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Snail's Reverie</t>
+          <t>Mộng Ảo Ốc Sên</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Wreck of Despair</t>
+          <t>Tàn Tích Tuyệt Vọng</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -8974,7 +8974,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Incendiary Surge</t>
+          <t>Làn Sóng Bùng Cháy</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9044,7 +9044,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Shattered Dreams</t>
+          <t>Giấc Mộng Tan Vỡ</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Glass Labyrinth</t>
+          <t>Mê Cung Pha Lê</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Blackened Blade</t>
+          <t>Lưỡi Kiếm Cháy Đen</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Turtle's Reverie</t>
+          <t>Giấc Mơ Rùa</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Rabbit's Reverie</t>
+          <t>Mộng Ảo Của Rabbit</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Innocent's Reverie</t>
+          <t>Mộng Ảo Ngây Thơ</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Lark's Reverie</t>
+          <t>Khúc Mộng Sơn Ca</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Snail's Reverie</t>
+          <t>Mộng Ảo Ốc Sên</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -9604,7 +9604,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Wreck of Despair</t>
+          <t>Tàn Tích Tuyệt Vọng</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Incendiary Surge</t>
+          <t>Làn Sóng Bùng Cháy</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -9744,7 +9744,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Shattered Dreams</t>
+          <t>Giấc Mộng Tan Vỡ</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Glass Labyrinth</t>
+          <t>Mê Cung Pha Lê</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -9884,7 +9884,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Blackened Blade</t>
+          <t>Lưỡi Kiếm Cháy Đen</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Traces of Mt. Firmament I</t>
+          <t>Dấu vết Núi Firmament I</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -10094,7 +10094,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Traces of Mt. Firmament II</t>
+          <t>Dấu vết Núi Firmament II</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -10164,7 +10164,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Traces of Mt. Firmament III</t>
+          <t>Dấu vết Núi Firmament III</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -10234,7 +10234,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Traces of Mt. Firmament IV</t>
+          <t>Dấu vết Núi Firmament IV</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Traces of Mt. Firmament V</t>
+          <t>Dấu vết Núi Firmament V</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Traces of Mt. Firmament VI</t>
+          <t>Dấu vết Núi Firmament VI</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Traces of Mt. Firmament VII</t>
+          <t>Dấu vết Núi Firmament VII</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Traces of Mt. Firmament VIII</t>
+          <t>Dấu vết Núi Firmament VIII</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Traces of Mt. Firmament IX</t>
+          <t>Dấu vết Núi Firmament IX</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>The Black Shores</t>
+          <t>Bờ Biển Đen</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -10724,7 +10724,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Giữa các Vì Sao: I</t>
+          <t>Giữa Ngân Hà: I</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Giữa các Vì Sao: II</t>
+          <t>Giữa Ngân Hà: II</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -10864,7 +10864,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Giữa các Vì Sao: III</t>
+          <t>Giữa Ngân Hà: III</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Giữa các Vì Sao: IV</t>
+          <t>Giữa Ngân Hà: IV</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -11004,7 +11004,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Giữa các Vì Sao: V</t>
+          <t>Giữa Ngân Hà: V</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Giữa các Vì Sao: VI</t>
+          <t>Giữa Ngân Hà: VI</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Arrived</t>
+          <t>Đã đến nơi</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Speedy Resonance</t>
+          <t>Cộng Hưởng Tốc Độ</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11284,7 +11284,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Dodge Recovery</t>
+          <t>Phục hồi né tránh</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -11354,7 +11354,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Crit. Rate Up</t>
+          <t>Tăng Crit. Rate</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -11424,7 +11424,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Crit. DMG Up</t>
+          <t>Tăng Crit. DMG</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11494,7 +11494,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Damage Increase</t>
+          <t>Tăng Sát Thương</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11564,7 +11564,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Dream Đặt lại</t>
+          <t>Thiết Lập Lại Giấc Mơ</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11634,7 +11634,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Awakened Will</t>
+          <t>Ý Chí Thức Tỉnh</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -11704,7 +11704,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Accelerated Liberation</t>
+          <t>Giải Phóng Tăng Tốc</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>HP Up</t>
+          <t>Tăng HP</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>DEF Up</t>
+          <t>Tăng Phòng Ngự</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -11914,7 +11914,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>DMG Reduction</t>
+          <t>Giảm Sát Thương</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -11984,7 +11984,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Dreamworld Showdown</t>
+          <t>Đọ Sức Mộng Ảo</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -22624,7 +22624,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Interlude: I</t>
+          <t>Chương xen: Tôi</t>
         </is>
       </c>
       <c r="N317" t="inlineStr">
@@ -22764,7 +22764,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Prologue</t>
+          <t>Khúc dạo đầu</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
@@ -22834,7 +22834,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>The Black Shores</t>
+          <t>Bờ Biển Đen</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
@@ -22904,7 +22904,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Nhiệm Vụ Sự Kiện</t>
+          <t>Nhiệm vụ sự kiện</t>
         </is>
       </c>
       <c r="N321" t="inlineStr">
@@ -22974,7 +22974,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Chương II: Những Linh Hồn Câm Lặng Đều Có Thể Hát</t>
+          <t>Chương II: Những Linh Hồn Câm Lặng Vẫn Có Thể Hát</t>
         </is>
       </c>
       <c r="N322" t="inlineStr">
@@ -23394,7 +23394,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Lời Tuyên Ngôn Kỳ Diệu: Phần I</t>
+          <t>Lời Huyền Diệu: Phần I</t>
         </is>
       </c>
       <c r="N328" t="inlineStr">
@@ -23464,7 +23464,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Lời Tuyên Ngôn Kỳ Diệu: Phần II</t>
+          <t>Lời Huyền Diệu: Phần II</t>
         </is>
       </c>
       <c r="N329" t="inlineStr">
@@ -23534,7 +23534,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Resonance Đầu tiên</t>
+          <t>Cộng hưởng đầu tiên</t>
         </is>
       </c>
       <c r="N330" t="inlineStr">
@@ -23604,7 +23604,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Echoing Marche</t>
+          <t>Hành Quân Vang Vọng</t>
         </is>
       </c>
       <c r="N331" t="inlineStr">
@@ -23674,7 +23674,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Ngôi Sao Điềm Gở</t>
+          <t>Ngôi Sao U Ám</t>
         </is>
       </c>
       <c r="N332" t="inlineStr">
@@ -23744,7 +23744,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Kiếm Kích</t>
+          <t>Kiếm kích</t>
         </is>
       </c>
       <c r="N333" t="inlineStr">
@@ -23814,7 +23814,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Giọt Mưa Quay Ngược</t>
+          <t>Quay ngược Giọt Mưa Rơi</t>
         </is>
       </c>
       <c r="N334" t="inlineStr">
@@ -23884,7 +23884,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Grand Warstorm: Part I</t>
+          <t>Bão Chiến Lớn: Phần I</t>
         </is>
       </c>
       <c r="N335" t="inlineStr">
@@ -23954,7 +23954,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Grand Warstorm: Part II</t>
+          <t>Bão Chiến Lớn: Phần II</t>
         </is>
       </c>
       <c r="N336" t="inlineStr">
@@ -24024,7 +24024,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Người Bạn Mới</t>
+          <t>Người Bạn Đồng Hành Mới</t>
         </is>
       </c>
       <c r="N337" t="inlineStr">
@@ -24094,7 +24094,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Tan Băng Ngàn Năm</t>
+          <t>Thời Khắc Tan Băng</t>
         </is>
       </c>
       <c r="N338" t="inlineStr">
@@ -24164,7 +24164,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Đến Bờ Biển Cuối Cùng</t>
+          <t>Đến Bến Cuối Bờ</t>
         </is>
       </c>
       <c r="N339" t="inlineStr">
@@ -24234,7 +24234,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Khi Đêm Gõ Cửa</t>
+          <t>Khi Bóng Đêm Gõ Cửa</t>
         </is>
       </c>
       <c r="N340" t="inlineStr">
@@ -24304,7 +24304,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Vượt Qua Đại Dương Vĩ Đại</t>
+          <t>Xuyên qua Đại Dương Ngươi Đi</t>
         </is>
       </c>
       <c r="N341" t="inlineStr">
@@ -24374,7 +24374,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Làn Gió Thánh Thường Xuyên Thổi</t>
+          <t>Ngọn Gió Thiêng Thường Thở</t>
         </is>
       </c>
       <c r="N342" t="inlineStr">
@@ -24444,7 +24444,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Bức Màn Bị Kéo Lên Dù Nắng Hay Bóng Tối</t>
+          <t>Bỏ Màn Trong Nắng Hay Bóng Tối</t>
         </is>
       </c>
       <c r="N343" t="inlineStr">
@@ -24514,7 +24514,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Điều Hôm Qua Khóc Than, Hôm Nay Sẽ Hát Ca</t>
+          <t>Điều Hôm Qua Khóc Than, Hôm Nay Cất Lên Tiếng Hát</t>
         </is>
       </c>
       <c r="N344" t="inlineStr">
@@ -24584,7 +24584,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Ông Già và Cá Voi</t>
+          <t>Lão Già và Cá Voi</t>
         </is>
       </c>
       <c r="N345" t="inlineStr">
@@ -24654,7 +24654,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Thiếu Nữ, Kẻ Thách Thức, Người Rao Tin Tử Thần</t>
+          <t>Thánh Nữ, Kẻ Nổi Loạn, Kẻ Rao Tin Tử Thần</t>
         </is>
       </c>
       <c r="N346" t="inlineStr">
@@ -24724,7 +24724,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Cube, Cubic và Cubie</t>
+          <t>Khối, Khối Lập Phương và Cubie</t>
         </is>
       </c>
       <c r="N347" t="inlineStr">
@@ -24794,7 +24794,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Bóng Tối Của Vinh Quang</t>
+          <t>Bóng Tối Vinh Quang</t>
         </is>
       </c>
       <c r="N348" t="inlineStr">
@@ -24864,7 +24864,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Ngọn Lửa Trái Tim</t>
+          <t>Lửa Của Trái Tim</t>
         </is>
       </c>
       <c r="N349" t="inlineStr">
@@ -24934,7 +24934,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Rạng Đông Cuối Cùng</t>
+          <t>Cuối Cùng Cũng Bình Minh</t>
         </is>
       </c>
       <c r="N350" t="inlineStr">
@@ -25004,7 +25004,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Trở về của Trái Tim Hoang Dã</t>
+          <t>Trở Về Của Trái Tim Hoang Dã</t>
         </is>
       </c>
       <c r="N351" t="inlineStr">
@@ -25074,7 +25074,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Con Đường Cô Đơn</t>
+          <t>Con Đường Cô Độc</t>
         </is>
       </c>
       <c r="N352" t="inlineStr">
@@ -25144,7 +25144,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Lửa Bất Tử</t>
+          <t>Lửa Bất Diệt</t>
         </is>
       </c>
       <c r="N353" t="inlineStr">
@@ -25214,7 +25214,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Prologue</t>
+          <t>Khúc dạo đầu</t>
         </is>
       </c>
       <c r="N354" t="inlineStr">
@@ -25284,7 +25284,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Prologue</t>
+          <t>Khúc dạo đầu</t>
         </is>
       </c>
       <c r="N355" t="inlineStr">
@@ -25844,7 +25844,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Interlude</t>
+          <t>Khúc Tạm Ngừng</t>
         </is>
       </c>
       <c r="N363" t="inlineStr">
@@ -26054,7 +26054,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Interlude</t>
+          <t>Khúc Tạm Ngừng</t>
         </is>
       </c>
       <c r="N366" t="inlineStr">
@@ -26124,7 +26124,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Chương II Lời Mở Đầu</t>
+          <t>Lời Mở Đầu Chương II</t>
         </is>
       </c>
       <c r="N367" t="inlineStr">
@@ -26404,7 +26404,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Interlude</t>
+          <t>Khúc Tạm Ngừng</t>
         </is>
       </c>
       <c r="N371" t="inlineStr">
@@ -26544,7 +26544,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Interlude</t>
+          <t>Khúc Tạm Ngừng</t>
         </is>
       </c>
       <c r="N373" t="inlineStr">
@@ -27034,7 +27034,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Main Quests</t>
+          <t>Nhiệm Vụ Chính</t>
         </is>
       </c>
       <c r="N380" t="inlineStr">
@@ -27104,7 +27104,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Companion Stories</t>
+          <t>Câu Chuyện Đồng Hành</t>
         </is>
       </c>
       <c r="N381" t="inlineStr">
@@ -27174,7 +27174,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Main Story</t>
+          <t>Câu Chuyện Chính</t>
         </is>
       </c>
       <c r="N382" t="inlineStr">
@@ -27244,7 +27244,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Glitters</t>
+          <t>Những Tia Lấp Lánh</t>
         </is>
       </c>
       <c r="N383" t="inlineStr">
@@ -27314,7 +27314,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Sparkles</t>
+          <t>Tia Lấp Lánh</t>
         </is>
       </c>
       <c r="N384" t="inlineStr">
@@ -27384,7 +27384,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Time Stilling</t>
+          <t>Thời gian ngưng đọng</t>
         </is>
       </c>
       <c r="N385" t="inlineStr">
@@ -27454,7 +27454,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Celestial Walker</t>
+          <t>Thiên Hành Giả</t>
         </is>
       </c>
       <c r="N386" t="inlineStr">
@@ -27664,7 +27664,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Dampening Joy</t>
+          <t>Niềm Vui Câm Lặng</t>
         </is>
       </c>
       <c r="N389" t="inlineStr">
@@ -27734,7 +27734,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Diminishing Strength</t>
+          <t>Sức Mạnh Suy Yếu</t>
         </is>
       </c>
       <c r="N390" t="inlineStr">
@@ -27804,7 +27804,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Tactical Maneuver</t>
+          <t>Thủ Thuật Chiến Thuật</t>
         </is>
       </c>
       <c r="N391" t="inlineStr">
@@ -27874,7 +27874,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Vươn Lên Từ Tro Tàn</t>
+          <t>Trỗi Dậy Từ Tro Tàn</t>
         </is>
       </c>
       <c r="N392" t="inlineStr">
@@ -27944,7 +27944,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Không thể chọn các Resonator giống nhau</t>
+          <t>Không thể chọn các Resonator trùng lặp</t>
         </is>
       </c>
       <c r="N393" t="inlineStr">
@@ -28014,7 +28014,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Thử Thách Bị Khóa</t>
+          <t>Thử Thách Đã Khóa</t>
         </is>
       </c>
       <c r="N394" t="inlineStr">
@@ -28084,7 +28084,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Sự Kiện Đã Kết Thúc</t>
+          <t>Sự kiện đã kết thúc</t>
         </is>
       </c>
       <c r="N395" t="inlineStr">
@@ -28154,7 +28154,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Snow Moon Flower Spinner</t>
+          <t>Bông Tuyết Trăng Hoa</t>
         </is>
       </c>
       <c r="N396" t="inlineStr">
@@ -28224,7 +28224,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Perpetual Dance</t>
+          <t>Điệu Nhảy Vĩnh Hằng</t>
         </is>
       </c>
       <c r="N397" t="inlineStr">
@@ -28294,7 +28294,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Centrifugal Acceleration</t>
+          <t>Gia Tốc Ly Tâm</t>
         </is>
       </c>
       <c r="N398" t="inlineStr">
@@ -28364,7 +28364,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Vua Nhạc Disco</t>
+          <t>Vua Nhịp Điệu</t>
         </is>
       </c>
       <c r="N399" t="inlineStr">
@@ -28434,7 +28434,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Fantasy Renewed</t>
+          <t>Ảo Ảnh Phục Sinh</t>
         </is>
       </c>
       <c r="N400" t="inlineStr">
@@ -28504,7 +28504,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Ultimate Glacio Echo</t>
+          <t>Tiếng Vọng Glacio Tối Thượng</t>
         </is>
       </c>
       <c r="N401" t="inlineStr">
@@ -28574,7 +28574,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Heavenly Subjugation</t>
+          <t>Thiên Quy Phục</t>
         </is>
       </c>
       <c r="N402" t="inlineStr">
@@ -28644,7 +28644,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Grand Crimson Lotus</t>
+          <t>Đại Liên Hoa Đỏ Thẫm</t>
         </is>
       </c>
       <c r="N403" t="inlineStr">
@@ -28714,7 +28714,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Đứng Trên Bầu Trời Băng Giá</t>
+          <t>Đứng Trên Thiên Đường Băng Giá</t>
         </is>
       </c>
       <c r="N404" t="inlineStr">
@@ -28784,7 +28784,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Four-Realm Freeze</t>
+          <t>Băng Giá Tứ Giới</t>
         </is>
       </c>
       <c r="N405" t="inlineStr">
@@ -28854,7 +28854,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Form Unleashed</t>
+          <t>Hình Thái Giải Phóng</t>
         </is>
       </c>
       <c r="N406" t="inlineStr">
@@ -28994,7 +28994,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Ta Chọn Hình Dạng Tự Động Hóa</t>
+          <t>Ta chọn hình dạng cho Autopuppet.</t>
         </is>
       </c>
       <c r="N408" t="inlineStr">
@@ -29064,7 +29064,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Coolest Cooler</t>
+          <t>Bậc thầy làm mát</t>
         </is>
       </c>
       <c r="N409" t="inlineStr">
@@ -29134,7 +29134,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Industrial HVAC</t>
+          <t>Hệ Thống Điều Hòa Công Nghiệp</t>
         </is>
       </c>
       <c r="N410" t="inlineStr">
@@ -29204,7 +29204,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Man-Made Arctic</t>
+          <t>Bắc Cực Nhân Tạo</t>
         </is>
       </c>
       <c r="N411" t="inlineStr">
@@ -29274,7 +29274,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Blue Cosmos Drifter</t>
+          <t>Kẻ Lang Thang Càn Khôn Xanh</t>
         </is>
       </c>
       <c r="N412" t="inlineStr">
@@ -29414,7 +29414,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Nuclear Reactor</t>
+          <t>Lò phản ứng hạt nhân</t>
         </is>
       </c>
       <c r="N414" t="inlineStr">
@@ -29484,7 +29484,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Assembly Line</t>
+          <t>Dây Chuyền Lắp Ráp</t>
         </is>
       </c>
       <c r="N415" t="inlineStr">
@@ -29554,7 +29554,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Vì Thế Giới Xanh Tinh Khiết Của Chúng Ta</t>
+          <t>Vì Thế Giới Xanh Trong Của Chúng Ta</t>
         </is>
       </c>
       <c r="N416" t="inlineStr">
@@ -29624,7 +29624,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Mass Production Suits</t>
+          <t>Bộ giáp Sản Xuất Hàng Loạt</t>
         </is>
       </c>
       <c r="N417" t="inlineStr">
@@ -29694,7 +29694,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>"R" Button Presser</t>
+          <t>"Người nhấn nút R"</t>
         </is>
       </c>
       <c r="N418" t="inlineStr">
@@ -29834,7 +29834,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Rock Solid</t>
+          <t>Vững Như Đá</t>
         </is>
       </c>
       <c r="N420" t="inlineStr">
@@ -29904,7 +29904,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Brain Turned Off</t>
+          <t>Não Tắt Ngúm</t>
         </is>
       </c>
       <c r="N421" t="inlineStr">
@@ -29974,7 +29974,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Giữa Đá Và Nơi Khó Khăn</t>
+          <t>Giữa Đá và Nước Sôi</t>
         </is>
       </c>
       <c r="N422" t="inlineStr">
@@ -30044,7 +30044,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Những Linh Hồn Bị Trọng Lực Đè Nặng</t>
+          <t>Những Linh Hồn Bị Trọng Lực Kìm Kẹp</t>
         </is>
       </c>
       <c r="N423" t="inlineStr">
@@ -30114,7 +30114,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Universal Gravitation</t>
+          <t>Trọng Lực Vũ Trụ</t>
         </is>
       </c>
       <c r="N424" t="inlineStr">
@@ -30184,7 +30184,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Space Repercussion</t>
+          <t>Hậu Quả Không Gian</t>
         </is>
       </c>
       <c r="N425" t="inlineStr">
@@ -30254,7 +30254,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Hedgehog's Dilemma</t>
+          <t>Nghịch Lý Nhím</t>
         </is>
       </c>
       <c r="N426" t="inlineStr">
@@ -30324,7 +30324,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Supergravity Field</t>
+          <t>Trường Siêu Trọng Lực</t>
         </is>
       </c>
       <c r="N427" t="inlineStr">
@@ -30394,7 +30394,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Beyond Time</t>
+          <t>Vượt Qua Thời Gian</t>
         </is>
       </c>
       <c r="N428" t="inlineStr">
@@ -30464,7 +30464,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Trying-Too-Khó Vocalist</t>
+          <t>Ca Sĩ Cố Gắng Quá Sức</t>
         </is>
       </c>
       <c r="N429" t="inlineStr">
@@ -30674,7 +30674,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Handwritten Notebook</t>
+          <t>Sổ Tay Viết Tay</t>
         </is>
       </c>
       <c r="N432" t="inlineStr">
@@ -30744,7 +30744,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>A Doll's Wish</t>
+          <t>Ước Nguyện Của Búp Bê</t>
         </is>
       </c>
       <c r="N433" t="inlineStr">
@@ -30814,7 +30814,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Ánh Nắng Mùa Xuân</t>
+          <t>Ánh Xuân</t>
         </is>
       </c>
       <c r="N434" t="inlineStr">
@@ -30884,7 +30884,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>"Meow Are #2"</t>
+          <t>"Meo Are #2"</t>
         </is>
       </c>
       <c r="N435" t="inlineStr">
@@ -30954,7 +30954,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Helm Breaker</t>
+          <t>Phá Vỡ Đầu Giáp</t>
         </is>
       </c>
       <c r="N436" t="inlineStr">
@@ -31024,7 +31024,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Sakura Strike</t>
+          <t>Đòn Sakura</t>
         </is>
       </c>
       <c r="N437" t="inlineStr">
@@ -31094,7 +31094,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Serenity Stance</t>
+          <t>Thế Trấn Tĩnh</t>
         </is>
       </c>
       <c r="N438" t="inlineStr">
@@ -31164,7 +31164,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Jumping Spirit Blade</t>
+          <t>Kiếm Linh Hồn Nhảy Xuất</t>
         </is>
       </c>
       <c r="N439" t="inlineStr">
@@ -31234,7 +31234,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Iai Slash</t>
+          <t>Đòn chém Iai</t>
         </is>
       </c>
       <c r="N440" t="inlineStr">
@@ -31304,7 +31304,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>"Ngươi Còn Rồng Hơn Ta"</t>
+          <t>"Ngươi mới là Rồng thực sự"</t>
         </is>
       </c>
       <c r="N441" t="inlineStr">
@@ -31374,7 +31374,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Than Hồng Lụi Tàn</t>
+          <t>Lửa Than Tàn Lụi</t>
         </is>
       </c>
       <c r="N442" t="inlineStr">
@@ -31444,7 +31444,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Những Kẻ Canh Gác Vực Thẳm</t>
+          <t>Những Người Quan Sát Vực Thẳm</t>
         </is>
       </c>
       <c r="N443" t="inlineStr">
@@ -31514,7 +31514,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Ancient Dragon Form</t>
+          <t>Hình Thái Rồng Cổ Đại</t>
         </is>
       </c>
       <c r="N444" t="inlineStr">
@@ -31584,7 +31584,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Undead Dancers Legion</t>
+          <t>Đoàn Vũ Công Bất Tử</t>
         </is>
       </c>
       <c r="N445" t="inlineStr">
@@ -31654,7 +31654,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Chúa Tể Than Đỏ</t>
+          <t>Chúa Tể Than Hồng</t>
         </is>
       </c>
       <c r="N446" t="inlineStr">
@@ -31724,7 +31724,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Recovery Paused</t>
+          <t>Tạm dừng hồi phục</t>
         </is>
       </c>
       <c r="N447" t="inlineStr">
@@ -31794,7 +31794,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Maxed Out</t>
+          <t>Đã đạt tối đa</t>
         </is>
       </c>
       <c r="N448" t="inlineStr">
@@ -31864,7 +31864,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Waveplate Đã Đầy</t>
+          <t>Bảng Tần Số đã đầy</t>
         </is>
       </c>
       <c r="N449" t="inlineStr">
@@ -31934,7 +31934,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Insufficient Waveplate Crystals</t>
+          <t>Không đủ Tinh Thể Waveplate.</t>
         </is>
       </c>
       <c r="N450" t="inlineStr">
@@ -32144,7 +32144,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Đăng Nhập</t>
+          <t>Đăng nhập</t>
         </is>
       </c>
       <c r="N453" t="inlineStr">
@@ -32214,7 +32214,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Available</t>
+          <t>Có Sẵn</t>
         </is>
       </c>
       <c r="N454" t="inlineStr">
@@ -32284,7 +32284,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Collected</t>
+          <t>Đã thu thập</t>
         </is>
       </c>
       <c r="N455" t="inlineStr">
@@ -32354,7 +32354,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>New Rarity Unlocked</t>
+          <t>Độ Hiếm Mới đã mở khóa</t>
         </is>
       </c>
       <c r="N456" t="inlineStr">
@@ -32424,7 +32424,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>New Phantom Echo Unlocked</t>
+          <t>Hồi Âm Ảo Mới đã mở khóa</t>
         </is>
       </c>
       <c r="N457" t="inlineStr">
@@ -32494,7 +32494,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>ATK Up</t>
+          <t>Tăng ATK</t>
         </is>
       </c>
       <c r="N458" t="inlineStr">
@@ -32564,7 +32564,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Phước Lành Giấc Mơ</t>
+          <t>Phúc Lành Giấc Mơ</t>
         </is>
       </c>
       <c r="N459" t="inlineStr">
@@ -32634,7 +32634,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Dream Đặt lại II</t>
+          <t>Đặt Lại Giấc Mơ II</t>
         </is>
       </c>
       <c r="N460" t="inlineStr">
@@ -32704,7 +32704,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Dream Residue</t>
+          <t>Dư Vị Giấc Mơ</t>
         </is>
       </c>
       <c r="N461" t="inlineStr">
@@ -32774,7 +32774,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>test\Hồi sinh</t>
+          <t>Hồi sinh</t>
         </is>
       </c>
       <c r="N462" t="inlineStr">
@@ -32844,7 +32844,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>test\Hồi máu phòng</t>
+          <t>Phục hồi HP trong phòng</t>
         </is>
       </c>
       <c r="N463" t="inlineStr">
@@ -32914,7 +32914,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>test\Mỗi khi vào phòng, phục hồi 5% HP</t>
+          <t>Mỗi khi bước vào phòng, HP của ngươi sẽ hồi phục 5%</t>
         </is>
       </c>
       <c r="N464" t="inlineStr">
@@ -32984,7 +32984,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Mô Tả</t>
+          <t>Mô tả</t>
         </is>
       </c>
       <c r="N465" t="inlineStr">
@@ -33054,7 +33054,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Owned:</t>
+          <t>Đã chiếm giữ:</t>
         </is>
       </c>
       <c r="N466" t="inlineStr">
@@ -33124,7 +33124,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Độ khó Hiện tại</t>
+          <t>Mức Độ Khó Hiện Tại</t>
         </is>
       </c>
       <c r="N467" t="inlineStr">
@@ -33264,7 +33264,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Điều tra Dị thường</t>
+          <t>Điều tra dị thường</t>
         </is>
       </c>
       <c r="N469" t="inlineStr">
@@ -33404,7 +33404,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Bridged Dreamscape: Verina</t>
+          <t>Giấc Mộng Kết Nối: Verina</t>
         </is>
       </c>
       <c r="N471" t="inlineStr">
@@ -33474,7 +33474,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Bridged Dreamscape: Mortefi</t>
+          <t>Giấc Mộng Kết Nối: Mortefi</t>
         </is>
       </c>
       <c r="N472" t="inlineStr">
@@ -33544,7 +33544,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Bridged Dreamscape: Sanhua</t>
+          <t>Giấc Mộng Kết Nối: Sanhua</t>
         </is>
       </c>
       <c r="N473" t="inlineStr">
@@ -33614,7 +33614,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Bridged Dreamscape: Yuanwu</t>
+          <t>Giấc Mộng Kết Nối: Yuanwu</t>
         </is>
       </c>
       <c r="N474" t="inlineStr">
@@ -33684,7 +33684,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Bridged Dreamscape: Baizhi</t>
+          <t>Giấc Mộng Kết Nối: Baizhi</t>
         </is>
       </c>
       <c r="N475" t="inlineStr">
@@ -33754,7 +33754,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Bridged Dreamscape: Danjin</t>
+          <t>Giấc Mộng Kết Nối: Danjin</t>
         </is>
       </c>
       <c r="N476" t="inlineStr">
@@ -33824,7 +33824,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Bridged Dreamscape: Yinlin</t>
+          <t>Giấc Mộng Kết Nối: Yinlin</t>
         </is>
       </c>
       <c r="N477" t="inlineStr">
@@ -33894,7 +33894,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Bridged Dreamscape: Aalto</t>
+          <t>Giấc Mộng Kết Nối: Aalto</t>
         </is>
       </c>
       <c r="N478" t="inlineStr">
@@ -33964,7 +33964,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Bridged Dreamscape: Jianxin</t>
+          <t>Giấc Mộng Kết Nối: Jianxin</t>
         </is>
       </c>
       <c r="N479" t="inlineStr">
@@ -34034,7 +34034,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Refresh Cửa hàng</t>
+          <t>Làm mới Cửa Hàng</t>
         </is>
       </c>
       <c r="N480" t="inlineStr">
@@ -34104,7 +34104,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Vật Phẩm Không Có Sẵn Để Mua</t>
+          <t>Không thể mua vật phẩm này</t>
         </is>
       </c>
       <c r="N481" t="inlineStr">
@@ -34174,7 +34174,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Attack</t>
+          <t>Tấn Công</t>
         </is>
       </c>
       <c r="N482" t="inlineStr">
@@ -34244,7 +34244,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Điều Khiển</t>
         </is>
       </c>
       <c r="N483" t="inlineStr">
@@ -34384,7 +34384,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Bắt đầu lại</t>
         </is>
       </c>
       <c r="N485" t="inlineStr">
@@ -34454,7 +34454,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Hoàn Thành 1 Chương Nhiệm Vụ Chính (Có thể hoàn thành tối đa 3 lần)</t>
+          <t>Hoàn thành 1 Chương Nhiệm Vụ Chính (Có thể hoàn thành tối đa 3 lần)</t>
         </is>
       </c>
       <c r="N486" t="inlineStr">
@@ -34524,7 +34524,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Hoàn Thành 1 Chương Câu Chuyện Đồng Hành (Có thể hoàn thành tối đa 3 lần)</t>
+          <t>Hoàn thành 1 Chương Câu Chuyện Đồng Hành (Có thể hoàn thành tối đa 3 lần)</t>
         </is>
       </c>
       <c r="N487" t="inlineStr">
@@ -34594,7 +34594,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Mở 3 Rương Đồ Cung Ứng</t>
+          <t>Mở 3 Rương Cung Ứng</t>
         </is>
       </c>
       <c r="N488" t="inlineStr">
@@ -34664,7 +34664,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Thu Thập 2 Rương Sonance</t>
+          <t>Thu thập 2 Rương Thanh Âm</t>
         </is>
       </c>
       <c r="N489" t="inlineStr">
@@ -34734,7 +34734,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Tiêu Hết Tổng Cộng 120 Waveplate</t>
+          <t>Tổng cộng tiêu thụ 120 Tấm Năng Lượng.</t>
         </is>
       </c>
       <c r="N490" t="inlineStr">
@@ -34804,7 +34804,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Đăng nhập 7 ngày</t>
+          <t>Đăng Nhập 7 Ngày</t>
         </is>
       </c>
       <c r="N491" t="inlineStr">
@@ -34874,7 +34874,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Homecoming Quests</t>
+          <t>Nhiệm Vụ Trở Về</t>
         </is>
       </c>
       <c r="N492" t="inlineStr">
@@ -34944,7 +34944,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Wutherium Geographic</t>
+          <t>Địa lý Wutherium</t>
         </is>
       </c>
       <c r="N493" t="inlineStr">
@@ -35014,7 +35014,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Wuthering Triệu Tập</t>
+          <t>Hội Tụ Vực Gió</t>
         </is>
       </c>
       <c r="N494" t="inlineStr">
@@ -35084,7 +35084,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Nhiệm Vụ Người Quay Trở Lại</t>
+          <t>Nhiệm Vụ Người Trở Về</t>
         </is>
       </c>
       <c r="N495" t="inlineStr">
@@ -35154,7 +35154,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Tan Băng Ngàn Năm</t>
+          <t>Thời Khắc Tan Băng</t>
         </is>
       </c>
       <c r="N496" t="inlineStr">
@@ -35224,7 +35224,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Huanglong I - Act VII</t>
+          <t>Huanglong I - Hồi VII</t>
         </is>
       </c>
       <c r="N497" t="inlineStr">
@@ -35434,7 +35434,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Coming Soon</t>
+          <t>Sắp ra mắt</t>
         </is>
       </c>
       <c r="N500" t="inlineStr">
@@ -35504,7 +35504,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Phần Thưởng Lớn Có Sẵn Để Nhận</t>
+          <t>Phần thưởng lớn sẵn sàng để nhận</t>
         </is>
       </c>
       <c r="N501" t="inlineStr">
